--- a/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0001T0006Z000C1N56_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0001T0006Z000C1N56_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>8.077747210701755</v>
+        <v>1.312633921739035</v>
       </c>
       <c r="D2" t="n">
-        <v>8.015251760844167</v>
+        <v>1.302478411137177</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3644646171168509</v>
+        <v>0.05922550028148832</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4264870162693279</v>
+        <v>0.06930414014376585</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>8.806676444935457</v>
+        <v>1.431084922302012</v>
       </c>
       <c r="D3" t="n">
-        <v>8.868225793382823</v>
+        <v>1.441086691424709</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3644646171168509</v>
+        <v>0.05922550028148832</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4264870162693279</v>
+        <v>0.06930414014376585</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
